--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation-subordonnee.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4181" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4181" uniqueCount="425">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -796,6 +796,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>Observation.statusCode</t>
   </si>
   <si>
@@ -838,8 +842,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Observation.interpretationCode</t>
@@ -6997,7 +7001,7 @@
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>254</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>74</v>
@@ -7005,10 +7009,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7064,25 +7068,25 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7102,10 +7106,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7128,13 +7132,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7185,7 +7189,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7205,10 +7209,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7231,7 +7235,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7264,7 +7268,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7282,7 +7286,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7302,10 +7306,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7328,7 +7332,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7381,7 +7385,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7401,10 +7405,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7460,25 +7464,25 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7498,10 +7502,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7524,7 +7528,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7577,7 +7581,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7597,10 +7601,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7623,7 +7627,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7656,25 +7660,25 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7694,10 +7698,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7720,7 +7724,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7753,25 +7757,25 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7791,10 +7795,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7821,7 +7825,7 @@
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7872,7 +7876,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7892,10 +7896,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7918,7 +7922,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7971,7 +7975,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7991,10 +7995,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8017,7 +8021,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -8070,7 +8074,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8090,10 +8094,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8116,7 +8120,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -8169,7 +8173,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8189,10 +8193,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8215,7 +8219,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -8268,7 +8272,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8288,10 +8292,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8314,7 +8318,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8367,7 +8371,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8387,10 +8391,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8413,7 +8417,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8466,7 +8470,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8486,10 +8490,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8512,7 +8516,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8553,7 +8557,7 @@
         <v>74</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
@@ -8563,7 +8567,7 @@
         <v>124</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8583,13 +8587,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
@@ -8611,10 +8615,10 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -8666,7 +8670,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8686,10 +8690,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8787,10 +8791,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8888,10 +8892,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8989,10 +8993,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9090,10 +9094,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9193,10 +9197,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9296,10 +9300,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9399,10 +9403,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9502,10 +9506,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9603,10 +9607,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9643,7 +9647,7 @@
         <v>74</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>74</v>
@@ -9662,7 +9666,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9680,7 +9684,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -9700,10 +9704,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9730,7 +9734,7 @@
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9781,7 +9785,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9801,10 +9805,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9831,12 +9835,12 @@
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
@@ -9882,7 +9886,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9902,10 +9906,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9981,7 +9985,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10001,10 +10005,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10027,7 +10031,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10080,7 +10084,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10100,10 +10104,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10126,7 +10130,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10179,7 +10183,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10199,10 +10203,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10225,7 +10229,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10278,7 +10282,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10298,10 +10302,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10324,7 +10328,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10377,7 +10381,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10397,10 +10401,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10423,7 +10427,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10476,7 +10480,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10496,10 +10500,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10522,7 +10526,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10575,7 +10579,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10595,10 +10599,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10621,7 +10625,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10674,7 +10678,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10694,10 +10698,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10720,7 +10724,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10773,7 +10777,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10793,10 +10797,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10819,7 +10823,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10872,7 +10876,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10892,10 +10896,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10918,7 +10922,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10971,7 +10975,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10991,10 +10995,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11017,7 +11021,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11070,7 +11074,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11090,13 +11094,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>74</v>
@@ -11118,10 +11122,10 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -11173,7 +11177,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11193,10 +11197,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11294,10 +11298,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11395,10 +11399,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11496,10 +11500,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11597,10 +11601,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11700,10 +11704,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11803,10 +11807,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11906,10 +11910,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12009,10 +12013,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12110,10 +12114,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12150,7 +12154,7 @@
         <v>74</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>74</v>
@@ -12169,7 +12173,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>74</v>
@@ -12187,7 +12191,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -12207,10 +12211,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12237,7 +12241,7 @@
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12288,7 +12292,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12308,10 +12312,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12338,12 +12342,12 @@
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12389,7 +12393,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12409,10 +12413,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12488,7 +12492,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12508,10 +12512,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12534,7 +12538,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12587,7 +12591,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12607,10 +12611,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12633,7 +12637,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12686,7 +12690,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12706,10 +12710,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12732,7 +12736,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12785,7 +12789,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12805,10 +12809,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12831,7 +12835,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12884,7 +12888,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12904,10 +12908,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12930,7 +12934,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12983,7 +12987,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13003,10 +13007,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13029,7 +13033,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13082,7 +13086,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13102,10 +13106,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13128,7 +13132,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13181,7 +13185,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13201,10 +13205,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13227,7 +13231,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13280,7 +13284,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13300,10 +13304,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13326,7 +13330,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13379,7 +13383,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13399,10 +13403,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13425,7 +13429,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13478,7 +13482,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13498,10 +13502,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13524,7 +13528,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13577,7 +13581,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13597,10 +13601,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13623,7 +13627,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13676,7 +13680,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13696,10 +13700,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13722,7 +13726,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13775,7 +13779,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13795,10 +13799,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13821,7 +13825,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -13874,7 +13878,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13894,10 +13898,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13920,11 +13924,11 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13975,7 +13979,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -13995,10 +13999,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14096,10 +14100,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14197,10 +14201,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14298,10 +14302,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14399,10 +14403,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14502,10 +14506,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14605,10 +14609,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14708,10 +14712,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14811,10 +14815,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14912,10 +14916,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14949,7 +14953,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>74</v>
@@ -14971,7 +14975,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>74</v>
@@ -14989,7 +14993,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15009,10 +15013,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15035,7 +15039,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15088,7 +15092,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
@@ -15108,10 +15112,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15134,7 +15138,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15187,7 +15191,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
